--- a/registration_forms/033_drumline_and_majorette_registration--registration_forms.xlsx
+++ b/registration_forms/033_drumline_and_majorette_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'9th',_'value':_'9th'}</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '9th', 'value': '9th'}</t>
+          <t>9th</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'10th',_'value':_'10th'}</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '10th', 'value': '10th'}</t>
+          <t>10th</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'11th',_'value':_'11th'}</t>
+          <t>11th</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '11th', 'value': '11th'}</t>
+          <t>11th</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'12th',_'value':_'12th'}</t>
+          <t>12th</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '12th', 'value': '12th'}</t>
+          <t>12th</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'snare',_'value':_'snare'}</t>
+          <t>snare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Snare', 'value': 'snare'}</t>
+          <t>Snare</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'b-flat',_'value':_'b-flat'}</t>
+          <t>b-flat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'B-flat', 'value': 'b-flat'}</t>
+          <t>B-flat</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'tenor',_'value':_'tenor'}</t>
+          <t>tenor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Tenor', 'value': 'tenor'}</t>
+          <t>Tenor</t>
         </is>
       </c>
     </row>
@@ -945,29 +945,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>instrument_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'other', 'value': 'other'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -996,29 +996,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'teacher',_'value':_'teacher'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher', 'value': 'teacher'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>confirmation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_1}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>confirmation_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_false,_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': False, 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
